--- a/analysis/tables/bloom.xlsx
+++ b/analysis/tables/bloom.xlsx
@@ -536,27 +536,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7638702021886198</v>
+        <v>0.6161886297654867</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1268213904523227</v>
+        <v>-0.09117411435018735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 0.764x - 0.127</t>
+          <t>y = 0.616x - 0.091</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>0.7642292533357955</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06029442217092444</v>
+        <v>0.06029442217092446</v>
       </c>
       <c r="I3" t="n">
-        <v>0.166024790715697</v>
+        <v>0.1479646165897073</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6370488117362971</v>
+        <v>0.5250145154152994</v>
       </c>
       <c r="K3" t="n">
         <v>0.1882842318177868</v>
@@ -577,27 +577,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7629168788216554</v>
+        <v>0.6112626948192624</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1250175382014682</v>
+        <v>-0.08407215585801098</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 0.763x - 0.125</t>
+          <t>y = 0.611x - 0.084</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.7644707871401335</v>
+        <v>0.7656324417913569</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06028782295564297</v>
+        <v>0.06025608408932925</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1638678362897947</v>
+        <v>0.137538502791945</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6378993406201872</v>
+        <v>0.5271905389612515</v>
       </c>
       <c r="K4" t="n">
         <v>0.1882842318177868</v>
